--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2456" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2456" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3544" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3544" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3592" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3592" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3880" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>

--- a/src/main/resources/data/ExpectedStations.xlsx
+++ b/src/main/resources/data/ExpectedStations.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3880" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4136" uniqueCount="17">
   <si>
     <t>Station</t>
   </si>
